--- a/output/pdf_financials_xlsx/ENGH.xlsx
+++ b/output/pdf_financials_xlsx/ENGH.xlsx
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>39.276</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>46.64</v>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>53.876</v>
+        <v>93.152</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>78.267</v>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>42.683</v>
+        <v>3.407</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>3.951</v>
@@ -22347,7 +22347,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">

--- a/output/pdf_financials_xlsx/ENGH.xlsx
+++ b/output/pdf_financials_xlsx/ENGH.xlsx
@@ -2031,25 +2031,25 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>1.102</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>1.386</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>1.743</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>2.315</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>3.438</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>2.437</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>2.411</v>
@@ -2058,22 +2058,22 @@
         <v>2.403</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>3.241</v>
+        <v>10.083</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>3.003</v>
+        <v>9.369</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>2.799</v>
+        <v>7.754</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.451</v>
+        <v>6.764</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>2.347</v>
+        <v>5.981</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2.518</v>
+        <v>5.644</v>
       </c>
     </row>
     <row r="29">
@@ -2089,25 +2089,25 @@
         <v>13.268</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>19.798</v>
+        <v>20.9</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.12</v>
+        <v>23.506</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>26.406</v>
+        <v>28.149</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>34.132</v>
+        <v>36.447</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>35.252</v>
+        <v>37.94</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>54.343</v>
+        <v>57.781</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>60.969</v>
+        <v>63.406</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>79.96899999999999</v>
@@ -2116,22 +2116,22 @@
         <v>84.846</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>124.3</v>
+        <v>131.142</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>110.207</v>
+        <v>116.573</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>97.845</v>
+        <v>102.8</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>83.41200000000001</v>
+        <v>87.72499999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>93.492</v>
+        <v>97.126</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>86.01600000000001</v>
+        <v>89.142</v>
       </c>
     </row>
     <row r="30">
@@ -2147,25 +2147,25 @@
         <v>14.08372961956522</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>16.15385243025808</v>
+        <v>17.05301120276765</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>16.22081426727678</v>
+        <v>17.23718174351754</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>14.67929688802909</v>
+        <v>15.6482438877956</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>15.51546227731639</v>
+        <v>16.56779718801566</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12.62096644266468</v>
+        <v>13.58332766466294</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>17.64480507040973</v>
+        <v>18.76110045034953</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>18.73847458877333</v>
+        <v>19.48747264635736</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>23.3251177645875</v>
@@ -2174,22 +2174,22 @@
         <v>21.98920314212926</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>24.67356653128958</v>
+        <v>26.03170444124198</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>23.5899883769963</v>
+        <v>24.95264107608037</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>22.88316942830081</v>
+        <v>24.04200334436428</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>18.37179696138073</v>
+        <v>19.32175092836911</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>18.60518800807952</v>
+        <v>19.32836489189162</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>17.24189080296184</v>
+        <v>17.86849690705944</v>
       </c>
     </row>
     <row r="31">
@@ -6311,49 +6311,49 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.102</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.386</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.743</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2.315</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>3.438</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>2.437</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>2.411</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>10.083</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>9.369</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>7.754</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>6.764</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>5.981</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>5.644</v>
       </c>
     </row>
     <row r="101">
@@ -24696,7 +24696,11 @@
           <t>Depreciation of right-of-use assets 14</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -27143,7 +27147,11 @@
           <t>Depreciation of right-of-use assets 12</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -31951,7 +31959,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -40411,7 +40423,11 @@
           <t>Depreciation of right-of-use assets 14</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -43722,7 +43738,11 @@
           <t>Depreciation of right-of-use assets 12</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -53715,7 +53735,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
